--- a/08_References/Form_Mau_Import_Checklist.xlsx
+++ b/08_References/Form_Mau_Import_Checklist.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C72038-EFC5-4DAA-972A-BF71131CFD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Checklists" sheetId="1" r:id="rId1"/>
-    <sheet name="Checklist_Items" sheetId="2" r:id="rId2"/>
-    <sheet name="Huong_dan" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Checklists" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Checklist_Items" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Huong_dan" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="415">
   <si>
     <t>checklist_code</t>
   </si>
@@ -52,6 +51,12 @@
     <t>PRE_PREG_01</t>
   </si>
   <si>
+    <t>Đánh giá sức khỏe &amp; yếu tố nguy cơ</t>
+  </si>
+  <si>
+    <t>Xem xét tiền sử mang thai, bệnh lý bản thân, gia đình và môi trường sống</t>
+  </si>
+  <si>
     <t>PRE_PREGNANCY</t>
   </si>
   <si>
@@ -70,39 +75,33 @@
     <t>PRE_PREG_02</t>
   </si>
   <si>
-    <t>Đánh giá sức khỏe &amp; yếu tố nguy cơ</t>
-  </si>
-  <si>
-    <t>Xem xét tiền sử mang thai, bệnh lý bản thân, gia đình và môi trường sống</t>
+    <t>Khám, xét nghiệm &amp; điều trị trước thai kỳ</t>
+  </si>
+  <si>
+    <t>Khám phụ khoa, kiểm soát bệnh mạn tính và rà soát thuốc đang dùng</t>
   </si>
   <si>
     <t>PRE_PREG_03</t>
   </si>
   <si>
-    <t>Khám, xét nghiệm &amp; điều trị trước thai kỳ</t>
-  </si>
-  <si>
-    <t>Khám phụ khoa, kiểm soát bệnh mạn tính và rà soát thuốc đang dùng</t>
+    <t>Điều chỉnh dinh dưỡng và lối sống</t>
+  </si>
+  <si>
+    <t>Chế độ ăn đa dạng, duy trì cân nặng hợp lý và vận động thể lực</t>
   </si>
   <si>
     <t>PRE_PREG_04</t>
   </si>
   <si>
-    <t>Điều chỉnh dinh dưỡng và lối sống</t>
-  </si>
-  <si>
-    <t>Chế độ ăn đa dạng, duy trì cân nặng hợp lý và vận động thể lực</t>
+    <t>Bổ sung vi chất &amp; hoàn thành tiêm chủng</t>
+  </si>
+  <si>
+    <t>Bổ sung sắt, axit folic và tiêm các vắc-xin cần thiết trước mang thai</t>
   </si>
   <si>
     <t>PRE_PREG_05</t>
   </si>
   <si>
-    <t>Bổ sung vi chất &amp; hoàn thành tiêm chủng</t>
-  </si>
-  <si>
-    <t>Bổ sung sắt, axit folic và tiêm các vắc-xin cần thiết trước mang thai</t>
-  </si>
-  <si>
     <t>Chuẩn bị sẵn sàng để thụ thai</t>
   </si>
   <si>
@@ -229,6 +228,18 @@
     <t>Bổ sung Axit Folic 600mcg/ngày từ tuần 21 đến khi sinh</t>
   </si>
   <si>
+    <t>PREG_DAILY_03</t>
+  </si>
+  <si>
+    <t>Vận động nhẹ nhàng &amp; giãn cơ hàng ngày cho mẹ bầu</t>
+  </si>
+  <si>
+    <t>Duy trì 20–30 phút vận động nhẹ nhàng mỗi ngày: đi bộ, bài tập thở, Kegel và kéo giãn giảm đau mỏi lưng hông</t>
+  </si>
+  <si>
+    <t>OPTIONAL</t>
+  </si>
+  <si>
     <t>POST_WEEK_01</t>
   </si>
   <si>
@@ -259,6 +270,15 @@
     <t>Khám sức khỏe toàn diện, đánh giá tâm thần và chăm sóc sức khỏe dài hạn</t>
   </si>
   <si>
+    <t>POST_DAILY_01</t>
+  </si>
+  <si>
+    <t>Vận động phục hồi &amp; chăm sóc sàn chậu hàng ngày sau sinh</t>
+  </si>
+  <si>
+    <t>Duy trì 10–20 phút vận động nhẹ nhàng: thở cơ hoành, bài tập Kegel phục hồi sàn chậu và đi bộ chậm rãi</t>
+  </si>
+  <si>
     <t>BABY_0_28D</t>
   </si>
   <si>
@@ -367,129 +387,132 @@
     <t>source_url</t>
   </si>
   <si>
+    <t>Xem xét tiền sử mang thai và sinh con trước</t>
+  </si>
+  <si>
+    <t>Xem xét đầy đủ tiền sử mang thai và sinh con trước đây.</t>
+  </si>
+  <si>
+    <t>https://vnpa.moh.gov.vn/wp-content/uploads/2026/05/QD-1139-Tai-lieu-huong-dan-cham-soc-SKSS.pdf</t>
+  </si>
+  <si>
+    <t>Xem xét tiền sử bệnh bản thân và gia đình</t>
+  </si>
+  <si>
+    <t>Xem xét tiền sử bệnh của bản thân và gia đình.</t>
+  </si>
+  <si>
+    <t>Đánh giá nguy cơ bệnh mạn tính và di truyền</t>
+  </si>
+  <si>
+    <t>Đánh giá nguy cơ bệnh mạn tính, bệnh di truyền, bệnh lây truyền qua đường tình dục và các nhiễm khuẩn.</t>
+  </si>
+  <si>
+    <t>Rà soát yếu tố nghề nghiệp và môi trường</t>
+  </si>
+  <si>
+    <t>Xem xét thuốc đã sử dụng, nghề nghiệp, môi trường sống, làm việc và tiếp xúc hóa chất độc hại.</t>
+  </si>
+  <si>
+    <t>Khám sức khỏe và khám phụ khoa định kỳ</t>
+  </si>
+  <si>
+    <t>Khám sức khỏe và khám phụ khoa định kỳ mỗi năm.</t>
+  </si>
+  <si>
     <t>APPOINTMENTS</t>
   </si>
   <si>
+    <t>Điều trị bệnh phụ khoa và nhiễm khuẩn (nếu có)</t>
+  </si>
+  <si>
+    <t>Điều trị bệnh phụ khoa, nhiễm khuẩn đường sinh sản và bệnh lây truyền qua đường tình dục nếu có.</t>
+  </si>
+  <si>
+    <t>Kiểm soát bệnh mạn tính tiền thai kỳ</t>
+  </si>
+  <si>
+    <t>Kiểm soát tăng huyết áp, bệnh tim mạch, đái tháo đường và các bệnh mạn tính nếu có.</t>
+  </si>
+  <si>
+    <t>Rà soát thuốc và thực phẩm chức năng đang dùng</t>
+  </si>
+  <si>
+    <t>Rà soát thuốc đang dùng; thông báo đầy đủ thuốc, vitamin và thực phẩm chức năng để được đánh giá.</t>
+  </si>
+  <si>
+    <t>Ăn uống đa dạng, đủ chất và sử dụng muối iod</t>
+  </si>
+  <si>
+    <t>Ăn đa dạng, đủ chất và sử dụng muối hoặc bột canh có iod.</t>
+  </si>
+  <si>
     <t>CONTENT_LIBRARY</t>
   </si>
   <si>
-    <t>Xem xét tiền sử mang thai và sinh con trước</t>
-  </si>
-  <si>
-    <t>Xem xét đầy đủ tiền sử mang thai và sinh con trước đây.</t>
+    <t>Duy trì cân nặng và chỉ số BMI hợp lý</t>
+  </si>
+  <si>
+    <t>Đạt và duy trì cân nặng phù hợp; tài liệu đưa ra BMI 18,5–24 kg/m².</t>
+  </si>
+  <si>
+    <t>MATERNAL_HEALTH_METRICS</t>
+  </si>
+  <si>
+    <t>Tập thể dục thường xuyên, nghỉ ngơi hợp lý</t>
+  </si>
+  <si>
+    <t>Tập thể dục thường xuyên; bố trí lao động và nghỉ ngơi hợp lý.</t>
+  </si>
+  <si>
+    <t>MATERNAL_EXERCISES</t>
+  </si>
+  <si>
+    <t>Tránh rượu bia, thuốc lá và chất kích thích</t>
+  </si>
+  <si>
+    <t>Không uống rượu bia, hút thuốc, sử dụng chất gây nghiện; tránh hít khói thuốc.</t>
+  </si>
+  <si>
+    <t>Tránh tiếp xúc hóa chất độc hại</t>
+  </si>
+  <si>
+    <t>Tránh hóa chất độc hại, thuốc mạnh và thực phẩm chức năng không rõ nguồn gốc.</t>
+  </si>
+  <si>
+    <t>Giữ vệ sinh và tẩy giun định kỳ</t>
+  </si>
+  <si>
+    <t>Giữ vệ sinh cá nhân, vệ sinh môi trường và tẩy giun 1–2 lần mỗi năm.</t>
+  </si>
+  <si>
+    <t>Bổ sung Sắt và Axit Folic trước thai kỳ</t>
+  </si>
+  <si>
+    <t>Bổ sung sắt 30–60 mg/ngày và axit folic 400–800 mcg/ngày, ít nhất 3 tháng trước khi có thai.</t>
+  </si>
+  <si>
+    <t>REMINDERS</t>
+  </si>
+  <si>
+    <t>Tư vấn Axit Folic liều cao nếu có tiền sử dị tật</t>
+  </si>
+  <si>
+    <t>Nếu từng có thai hoặc sinh con bị dị tật ống thần kinh, trao đổi với bác sĩ về axit folic 4 mg/ngày.</t>
+  </si>
+  <si>
+    <t>EXPERT_CONSULTATION</t>
+  </si>
+  <si>
+    <t>Rà soát lịch sử tiêm chủng cá nhân</t>
+  </si>
+  <si>
+    <t>Xác định mình đã từng tiêm các vắc-xin được khuyến cáo hay chưa và hoàn thành liều còn thiếu theo tư vấn.</t>
   </si>
   <si>
     <t>HEALTH_RECORDS</t>
   </si>
   <si>
-    <t>Xem xét tiền sử bệnh bản thân và gia đình</t>
-  </si>
-  <si>
-    <t>Xem xét tiền sử bệnh của bản thân và gia đình.</t>
-  </si>
-  <si>
-    <t>Đánh giá nguy cơ bệnh mạn tính và di truyền</t>
-  </si>
-  <si>
-    <t>Đánh giá nguy cơ bệnh mạn tính, bệnh di truyền, bệnh lây truyền qua đường tình dục và các nhiễm khuẩn.</t>
-  </si>
-  <si>
-    <t>Rà soát yếu tố nghề nghiệp và môi trường</t>
-  </si>
-  <si>
-    <t>Xem xét thuốc đã sử dụng, nghề nghiệp, môi trường sống, làm việc và tiếp xúc hóa chất độc hại.</t>
-  </si>
-  <si>
-    <t>Khám sức khỏe và khám phụ khoa định kỳ</t>
-  </si>
-  <si>
-    <t>Khám sức khỏe và khám phụ khoa định kỳ mỗi năm.</t>
-  </si>
-  <si>
-    <t>Điều trị bệnh phụ khoa và nhiễm khuẩn (nếu có)</t>
-  </si>
-  <si>
-    <t>Điều trị bệnh phụ khoa, nhiễm khuẩn đường sinh sản và bệnh lây truyền qua đường tình dục nếu có.</t>
-  </si>
-  <si>
-    <t>Kiểm soát bệnh mạn tính tiền thai kỳ</t>
-  </si>
-  <si>
-    <t>Kiểm soát tăng huyết áp, bệnh tim mạch, đái tháo đường và các bệnh mạn tính nếu có.</t>
-  </si>
-  <si>
-    <t>MATERNAL_HEALTH_METRICS</t>
-  </si>
-  <si>
-    <t>Rà soát thuốc và thực phẩm chức năng đang dùng</t>
-  </si>
-  <si>
-    <t>Rà soát thuốc đang dùng; thông báo đầy đủ thuốc, vitamin và thực phẩm chức năng để được đánh giá.</t>
-  </si>
-  <si>
-    <t>Ăn uống đa dạng, đủ chất và sử dụng muối iod</t>
-  </si>
-  <si>
-    <t>Ăn đa dạng, đủ chất và sử dụng muối hoặc bột canh có iod.</t>
-  </si>
-  <si>
-    <t>Duy trì cân nặng và chỉ số BMI hợp lý</t>
-  </si>
-  <si>
-    <t>Đạt và duy trì cân nặng phù hợp; tài liệu đưa ra BMI 18,5–24 kg/m².</t>
-  </si>
-  <si>
-    <t>Tập thể dục thường xuyên, nghỉ ngơi hợp lý</t>
-  </si>
-  <si>
-    <t>Tập thể dục thường xuyên; bố trí lao động và nghỉ ngơi hợp lý.</t>
-  </si>
-  <si>
-    <t>MATERNAL_EXERCISES</t>
-  </si>
-  <si>
-    <t>Tránh rượu bia, thuốc lá và chất kích thích</t>
-  </si>
-  <si>
-    <t>Không uống rượu bia, hút thuốc, sử dụng chất gây nghiện; tránh hít khói thuốc.</t>
-  </si>
-  <si>
-    <t>Tránh tiếp xúc hóa chất độc hại</t>
-  </si>
-  <si>
-    <t>Tránh hóa chất độc hại, thuốc mạnh và thực phẩm chức năng không rõ nguồn gốc.</t>
-  </si>
-  <si>
-    <t>Giữ vệ sinh và tẩy giun định kỳ</t>
-  </si>
-  <si>
-    <t>Giữ vệ sinh cá nhân, vệ sinh môi trường và tẩy giun 1–2 lần mỗi năm.</t>
-  </si>
-  <si>
-    <t>Bổ sung Sắt và Axit Folic trước thai kỳ</t>
-  </si>
-  <si>
-    <t>Bổ sung sắt 30–60 mg/ngày và axit folic 400–800 mcg/ngày, ít nhất 3 tháng trước khi có thai.</t>
-  </si>
-  <si>
-    <t>REMINDERS</t>
-  </si>
-  <si>
-    <t>Tư vấn Axit Folic liều cao nếu có tiền sử dị tật</t>
-  </si>
-  <si>
-    <t>Nếu từng có thai hoặc sinh con bị dị tật ống thần kinh, trao đổi với bác sĩ về axit folic 4 mg/ngày.</t>
-  </si>
-  <si>
-    <t>EXPERT_CONSULTATION</t>
-  </si>
-  <si>
-    <t>Rà soát lịch sử tiêm chủng cá nhân</t>
-  </si>
-  <si>
-    <t>Xác định mình đã từng tiêm các vắc-xin được khuyến cáo hay chưa và hoàn thành liều còn thiếu theo tư vấn.</t>
-  </si>
-  <si>
     <t>Tiêm các vắc-xin thiết yếu trước mang thai</t>
   </si>
   <si>
@@ -535,6 +558,9 @@
     <t>Khám thai định kỳ xác định vị trí và tình trạng thai ban đầu.</t>
   </si>
   <si>
+    <t>https://www.who.int/teams/maternal-newborn-child-adolescent-health-and-ageing/handbooks/programme-manager-s-handbook-mncah/recommendations-on-interventions-along-life-course/maternal</t>
+  </si>
+  <si>
     <t>Xét nghiệm haemoglobin phát hiện thiếu máu</t>
   </si>
   <si>
@@ -718,6 +744,39 @@
     <t>Uống Axit Folic 600mcg/ngày từ tuần 21 đến khi sinh.</t>
   </si>
   <si>
+    <t>Khởi động nhẹ nhàng và hít thở sâu (5 phút)</t>
+  </si>
+  <si>
+    <t>Xoay nhẹ khớp cổ chân, cổ tay, khớp vai; hít thở sâu bằng cơ hoành để cung cấp oxy cho mẹ và bé, làm ấm cơ thể.</t>
+  </si>
+  <si>
+    <t>Đi bộ nhẹ nhàng hoặc bài tập vận động vừa sức (15–20 phút)</t>
+  </si>
+  <si>
+    <t>Đi bộ trên mặt phẳng với giày vừa vặn hoặc thực hiện động tác yoga thai kỳ nhẹ nhàng; giữ nhịp thở đều, có thể vừa nói chuyện vừa tập.</t>
+  </si>
+  <si>
+    <t>https://www.acog.org/clinical/clinical-guidance/committee-opinion/articles/2020/04/physical-activity-and-exercise-during-pregnancy-and-the-postpartum-period</t>
+  </si>
+  <si>
+    <t>Bài tập co thắt cơ sàn chậu (Kegel) (5 phút)</t>
+  </si>
+  <si>
+    <t>Siết chặt cơ đáy chậu trong 3–5 giây rồi thả lỏng 5 giây. Lặp lại 10–15 lần để tăng cường nâng đỡ tử cung và hỗ trợ chuyển dạ thuận lợi.</t>
+  </si>
+  <si>
+    <t>Kéo giãn cơ lưng, hông và thư giãn thả lỏng</t>
+  </si>
+  <si>
+    <t>Nghiêng lườn, kéo giãn cơ lưng nhẹ nhàng (như tư thế con mèo - con bò nhẹ) để giảm áp lực cột sống thắt lưng và ngừa chuột rút.</t>
+  </si>
+  <si>
+    <t>Uống đủ nước và theo dõi dấu hiệu cơ thể</t>
+  </si>
+  <si>
+    <t>Uống 200–300ml nước trước và sau khi tập. Ngừng tập ngay nếu cảm thấy hoa mắt, chóng mặt, khó thở, co thắt tử cung hoặc ra huyết.</t>
+  </si>
+  <si>
     <t>Đánh giá tâm trạng &amp; sàng lọc trầm cảm sau sinh</t>
   </si>
   <si>
@@ -778,12 +837,45 @@
     <t>Tìm hiểu thêm về chăm sóc sức khỏe dài hạn và vận động phục hồi.</t>
   </si>
   <si>
+    <t>Hít thở sâu cơ hoành kích hoạt cơ cốt lõi (5 phút)</t>
+  </si>
+  <si>
+    <t>Nằm hoặc ngồi thẳng lưng thư giãn, hít sâu bằng mũi nở bụng, thở chậm ra bằng miệng kết hợp siết nhẹ cơ bụng sâu để hỗ trợ khép cơ bụng sau sinh.</t>
+  </si>
+  <si>
+    <t>Bài tập Kegel phục hồi cơ sàn chậu</t>
+  </si>
+  <si>
+    <t>Co siết cơ sàn chậu 3–5 giây rồi thả lỏng hoàn toàn. Thực hiện 2–3 hiệp, mỗi hiệp 10 lần giúp ngừa sa tạng chậu và cải thiện kiểm soát tiểu tiện.</t>
+  </si>
+  <si>
+    <t>Đi bộ chậm rãi quanh phòng hoặc khuôn viên (10–15 phút)</t>
+  </si>
+  <si>
+    <t>Vận động sớm nhẹ nhàng giúp kích thích nhu động ruột, giảm táo bón, ngăn ngừa thuyên tắc tĩnh mạch và hỗ trợ tinh thần thư thái.</t>
+  </si>
+  <si>
+    <t>Kéo giãn cơ cổ, vai và lưng trên</t>
+  </si>
+  <si>
+    <t>Xoay cổ nhẹ nhàng, mở rộng lồng ngực và hạ vai để giải tỏa co thắt cơ do tư thế bế và cúi người cho bé bú trong ngày.</t>
+  </si>
+  <si>
+    <t>Lắng nghe cơ thể và theo dõi vết may/vết mổ</t>
+  </si>
+  <si>
+    <t>Không mang vác nặng, tránh gập bụng đột ngột. Tạm dừng nếu sản dịch ra nhiều hơn, đỏ tươi trở lại hoặc cảm thấy đau nhức vết khâu.</t>
+  </si>
+  <si>
     <t>Khám và theo dõi sơ sinh</t>
   </si>
   <si>
     <t>Xác nhận trẻ được đánh giá hô hấp, thân nhiệt, bú/ngậm bắt vú, da/vàng da, rốn, cân nặng và khám toàn thân.</t>
   </si>
   <si>
+    <t>https://drmarie.edu.vn/wp-content/uploads/wpcfto_files/66fddfd926be72172548f4fac68be4d7HD%20Quoc%20Gia%20ve%20DVCSSKSS%202016.pdf</t>
+  </si>
+  <si>
     <t>Bú mẹ và giữ ấm</t>
   </si>
   <si>
@@ -1169,33 +1261,24 @@
   </si>
   <si>
     <t>• Mỗi lần import hỗ trợ tối đa 100 checklist hợp lệ, dung lượng file tối đa 5MB.</t>
-  </si>
-  <si>
-    <t>https://vnpa.moh.gov.vn/wp-content/uploads/2026/05/QD-1139-Tai-lieu-huong-dan-cham-soc-SKSS.pdf</t>
-  </si>
-  <si>
-    <t>https://www.who.int/teams/maternal-newborn-child-adolescent-health-and-ageing/handbooks/programme-manager-s-handbook-mncah/recommendations-on-interventions-along-life-course/maternal</t>
-  </si>
-  <si>
-    <t>https://drmarie.edu.vn/wp-content/uploads/wpcfto_files/66fddfd926be72172548f4fac68be4d7HD%20Quoc%20Gia%20ve%20DVCSSKSS%202016.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1611,9 +1694,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1626,7 +1709,7 @@
     <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="28.05" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1658,137 +1741,137 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I2" s="2">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="I3" s="2">
         <v>2</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I4" s="2">
         <v>3</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" s="2">
         <v>4</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>28</v>
@@ -1797,28 +1880,28 @@
         <v>29</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I6" s="2">
         <v>5</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
@@ -1832,7 +1915,7 @@
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
@@ -1841,16 +1924,16 @@
         <v>20</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -1864,7 +1947,7 @@
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2">
         <v>21</v>
@@ -1873,16 +1956,16 @@
         <v>25</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
@@ -1896,7 +1979,7 @@
         <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" s="2">
         <v>26</v>
@@ -1905,16 +1988,16 @@
         <v>29</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>40</v>
       </c>
@@ -1928,7 +2011,7 @@
         <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" s="2">
         <v>30</v>
@@ -1937,16 +2020,16 @@
         <v>33</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
@@ -1960,7 +2043,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F11" s="2">
         <v>36</v>
@@ -1969,16 +2052,16 @@
         <v>37</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
@@ -1992,7 +2075,7 @@
         <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2">
         <v>38</v>
@@ -2001,16 +2084,16 @@
         <v>39</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -2024,7 +2107,7 @@
         <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2">
         <v>40</v>
@@ -2039,10 +2122,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>53</v>
       </c>
@@ -2056,7 +2139,7 @@
         <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
@@ -2074,7 +2157,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>57</v>
       </c>
@@ -2088,7 +2171,7 @@
         <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2">
         <v>21</v>
@@ -2106,7 +2189,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>60</v>
       </c>
@@ -2120,7 +2203,7 @@
         <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F16" s="2">
         <v>30</v>
@@ -2138,7 +2221,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>63</v>
       </c>
@@ -2152,7 +2235,7 @@
         <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
@@ -2161,7 +2244,7 @@
         <v>20</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I17" s="2">
         <v>0</v>
@@ -2170,7 +2253,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>67</v>
       </c>
@@ -2184,7 +2267,7 @@
         <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F18" s="2">
         <v>21</v>
@@ -2202,7 +2285,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>70</v>
       </c>
@@ -2213,28 +2296,28 @@
         <v>72</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="I19" s="2">
         <v>0</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>74</v>
       </c>
@@ -2245,92 +2328,92 @@
         <v>76</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I20" s="2">
         <v>0</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G21" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I21" s="2">
         <v>0</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G22" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I22" s="2">
         <v>0</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>84</v>
       </c>
@@ -2341,28 +2424,28 @@
         <v>86</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="F23" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>87</v>
       </c>
@@ -2373,202 +2456,202 @@
         <v>89</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G25" s="2">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I25" s="2">
         <v>0</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G26" s="2">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I26" s="2">
         <v>0</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G27" s="2">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="G28" s="2">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I28" s="2">
         <v>0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G29" s="2">
         <v>52</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I29" s="2">
         <v>0</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F30" s="2">
         <v>52</v>
@@ -2577,33 +2660,33 @@
         <v>52</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I30" s="2">
         <v>0</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="G31" s="2">
         <v>52</v>
@@ -2615,34 +2698,110 @@
         <v>0</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" s="2">
+        <v>52</v>
+      </c>
+      <c r="G32" s="2">
+        <v>52</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2">
+        <v>52</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D99" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <autoFilter ref="A1:J31"/>
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" sqref="D10:D99">
       <formula1>"PRE_PREGNANCY,PREGNANCY,POSTPARTUM,BABY_CARE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E99" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D99">
+      <formula1>"PRE_PREGNANCY,PREGNANCY,POSTPARTUM,BABY_CARE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E99">
       <formula1>"MANDATORY,OPTIONAL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H99" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E99">
+      <formula1>"MANDATORY,OPTIONAL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H10:H99">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J99" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H99">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J10:J99">
+      <formula1>"NONE,WEEKLY,DAILY"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J2:J99">
       <formula1>"NONE,WEEKLY,DAILY"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G111"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G121"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -2653,30 +2812,30 @@
     <col min="7" max="7" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="28.05" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2684,20 +2843,20 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2705,20 +2864,20 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2726,20 +2885,20 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2747,453 +2906,453 @@
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2">
         <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2">
         <v>4</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2">
         <v>4</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="G13" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B14" s="2">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15" s="2">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2">
         <v>1</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2">
         <v>3</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B20" s="2">
         <v>5</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2">
         <v>1</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B23" s="2">
         <v>3</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B24" s="2">
         <v>4</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>30</v>
       </c>
@@ -3201,22 +3360,22 @@
         <v>1</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>30</v>
       </c>
@@ -3224,22 +3383,22 @@
         <v>2</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>30</v>
       </c>
@@ -3247,22 +3406,22 @@
         <v>3</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
@@ -3270,22 +3429,22 @@
         <v>4</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>30</v>
       </c>
@@ -3293,22 +3452,22 @@
         <v>5</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>34</v>
       </c>
@@ -3316,22 +3475,22 @@
         <v>1</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>34</v>
       </c>
@@ -3339,22 +3498,22 @@
         <v>2</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>37</v>
       </c>
@@ -3362,22 +3521,22 @@
         <v>1</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>37</v>
       </c>
@@ -3385,22 +3544,22 @@
         <v>2</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>37</v>
       </c>
@@ -3408,22 +3567,22 @@
         <v>3</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>37</v>
       </c>
@@ -3431,22 +3590,22 @@
         <v>4</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>40</v>
       </c>
@@ -3454,22 +3613,22 @@
         <v>1</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>40</v>
       </c>
@@ -3477,22 +3636,22 @@
         <v>2</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
@@ -3500,22 +3659,22 @@
         <v>3</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>40</v>
       </c>
@@ -3523,22 +3682,22 @@
         <v>4</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>43</v>
       </c>
@@ -3546,22 +3705,22 @@
         <v>1</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>43</v>
       </c>
@@ -3569,22 +3728,22 @@
         <v>2</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>43</v>
       </c>
@@ -3592,22 +3751,22 @@
         <v>3</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>46</v>
       </c>
@@ -3615,22 +3774,22 @@
         <v>1</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>46</v>
       </c>
@@ -3638,22 +3797,22 @@
         <v>2</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>46</v>
       </c>
@@ -3661,22 +3820,22 @@
         <v>3</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>46</v>
       </c>
@@ -3684,22 +3843,22 @@
         <v>4</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>49</v>
       </c>
@@ -3707,22 +3866,22 @@
         <v>1</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>49</v>
       </c>
@@ -3730,22 +3889,22 @@
         <v>2</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>49</v>
       </c>
@@ -3753,22 +3912,22 @@
         <v>3</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>53</v>
       </c>
@@ -3776,22 +3935,22 @@
         <v>1</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>53</v>
       </c>
@@ -3799,22 +3958,22 @@
         <v>2</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>57</v>
       </c>
@@ -3822,22 +3981,22 @@
         <v>1</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>60</v>
       </c>
@@ -3845,22 +4004,22 @@
         <v>1</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>63</v>
       </c>
@@ -3868,22 +4027,22 @@
         <v>1</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>67</v>
       </c>
@@ -3891,22 +4050,22 @@
         <v>1</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>70</v>
       </c>
@@ -3914,22 +4073,22 @@
         <v>1</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>70</v>
       </c>
@@ -3937,22 +4096,22 @@
         <v>2</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>70</v>
       </c>
@@ -3960,321 +4119,321 @@
         <v>3</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>199</v>
+        <v>247</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="59" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B59" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B60" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B61" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B62" s="2">
+        <v>2</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B63" s="2">
+        <v>3</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B64" s="2">
+        <v>1</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B65" s="2">
+        <v>2</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B66" s="2">
+        <v>3</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B67" s="2">
         <v>4</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B63" s="2">
+      <c r="C67" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B68" s="2">
         <v>1</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B64" s="2">
+      <c r="C68" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="69" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B69" s="2">
         <v>2</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B65" s="2">
+      <c r="C69" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="70" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B70" s="2">
         <v>3</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B66" s="2">
+      <c r="C70" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71" s="2">
         <v>4</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B67" s="2">
-        <v>1</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="2">
-        <v>2</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B69" s="2">
-        <v>3</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B70" s="2">
-        <v>4</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B71" s="2">
-        <v>5</v>
-      </c>
       <c r="C71" s="3" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="72" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>84</v>
       </c>
@@ -4282,22 +4441,22 @@
         <v>1</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>84</v>
       </c>
@@ -4305,22 +4464,22 @@
         <v>2</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="74" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>84</v>
       </c>
@@ -4328,22 +4487,22 @@
         <v>3</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="75" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>84</v>
       </c>
@@ -4351,1097 +4510,1333 @@
         <v>4</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="76" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B76" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="77" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B77" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="78" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B78" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="79" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B79" s="2">
+        <v>3</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="2">
         <v>4</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
+      <c r="C80" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="81" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="2">
+        <v>5</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B80" s="2">
+      <c r="G81" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="82" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B82" s="2">
         <v>1</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+      <c r="C82" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="83" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="2">
+        <v>2</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B81" s="2">
+      <c r="G83" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="84" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" s="2">
+        <v>3</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="85" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="2">
+        <v>4</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="86" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="2">
+        <v>1</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="87" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87" s="2">
         <v>2</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
+      <c r="C87" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="88" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="2">
+        <v>3</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B82" s="2">
-        <v>3</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+      <c r="G88" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="89" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B89" s="2">
+        <v>4</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B83" s="2">
-        <v>4</v>
-      </c>
-      <c r="C83" s="3" t="s">
+      <c r="G89" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B84" s="2">
-        <v>5</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B85" s="2">
-        <v>1</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B86" s="2">
-        <v>2</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B87" s="2">
-        <v>3</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B88" s="2">
-        <v>4</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B89" s="2">
-        <v>5</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B90" s="2">
         <v>1</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="91" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B91" s="2">
         <v>2</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="92" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B92" s="2">
         <v>3</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="93" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B93" s="2">
         <v>4</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="94" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B94" s="2">
         <v>5</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="95" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B95" s="2">
         <v>1</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="96" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B96" s="2">
         <v>2</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="97" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B97" s="2">
         <v>3</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="98" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B98" s="2">
         <v>4</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="99" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B99" s="2">
+        <v>5</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="100" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B100" s="2">
         <v>1</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B100" s="2">
+      <c r="C100" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="101" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B101" s="2">
         <v>2</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B101" s="2">
+      <c r="C101" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="102" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" s="2">
         <v>3</v>
       </c>
-      <c r="C101" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B102" s="2">
+      <c r="C102" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="103" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B103" s="2">
         <v>4</v>
       </c>
-      <c r="C102" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B103" s="2">
+      <c r="C103" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="104" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2">
         <v>5</v>
       </c>
-      <c r="C103" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B104" s="2">
-        <v>6</v>
-      </c>
       <c r="C104" s="3" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="105" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B105" s="2">
         <v>1</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="106" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B106" s="2">
         <v>2</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="107" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B107" s="2">
         <v>3</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="108" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B108" s="2">
         <v>4</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F108" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="G108" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="109" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B109" s="2">
+        <v>1</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="110" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2">
+        <v>2</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="111" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B111" s="2">
+        <v>3</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="112" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B112" s="2">
+        <v>4</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="113" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B113" s="2">
         <v>5</v>
       </c>
-      <c r="C109" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B110" s="2">
+      <c r="C113" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="114" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B114" s="2">
         <v>6</v>
       </c>
-      <c r="C110" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B111" s="2">
+      <c r="C114" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="115" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B115" s="2">
         <v>1</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>386</v>
+      <c r="C115" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="116" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B116" s="2">
+        <v>2</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="117" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B117" s="2">
+        <v>3</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="118" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B118" s="2">
+        <v>4</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F118" s="2"/>
+      <c r="G118" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="119" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B119" s="2">
+        <v>5</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="120" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B120" s="2">
+        <v>6</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="121" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B121" s="2">
+        <v>1</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G111" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="E2:E198" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <autoFilter ref="A1:G111"/>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" sqref="E10:E198">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F198" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E198">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F198">
+      <formula1>"HEALTH_RECORDS,MATERNAL_HEALTH_METRICS,MATERNAL_EXERCISES,APPOINTMENTS,REMINDERS,JOURNEY,BABY_CARE,EXPERT_CONSULTATION,CONTENT_LIBRARY,AI_TRIAGE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F2:F198">
       <formula1>"HEALTH_RECORDS,MATERNAL_HEALTH_METRICS,MATERNAL_EXERCISES,APPOINTMENTS,REMINDERS,JOURNEY,BABY_CARE,EXPERT_CONSULTATION,CONTENT_LIBRARY,AI_TRIAGE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="22.35" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>343</v>
+        <v>374</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="2" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="3" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>348</v>
+        <v>379</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="5" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>350</v>
+        <v>381</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="6" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="7" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="8" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="9" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>358</v>
+        <v>389</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="11" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>361</v>
+        <v>392</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="12" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>363</v>
+        <v>394</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="13" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>365</v>
+        <v>396</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="14" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="15" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="16" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="17" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="18" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="19" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="20" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="21" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="22" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="23" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="24" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="25" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>379</v>
+        <v>410</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="26" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="27" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="28" ht="17.55" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>383</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>